--- a/Research Logs/Dave/Research Log - Dave 13.xlsx
+++ b/Research Logs/Dave/Research Log - Dave 13.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="744" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4DED2E7-79ED-4285-BBF9-269511A9CAAD}"/>
+  <xr:revisionPtr revIDLastSave="781" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E2112BD-AB40-4B84-A064-0F5BEB7EA392}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="212">
   <si>
     <t>Date</t>
   </si>
@@ -735,6 +735,33 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=ph05xoJ06ZM</t>
+  </si>
+  <si>
+    <t>https://nmap.org/book/output.html</t>
+  </si>
+  <si>
+    <t>Figuring out what to report on in an Nmap scan</t>
+  </si>
+  <si>
+    <t>https://www.professormesser.com/nmap/deciphering-nmaps-port-descriptions/</t>
+  </si>
+  <si>
+    <t>https://roihacks.com/how-to-check-results-in-nmap/</t>
+  </si>
+  <si>
+    <t>https://nmap.org/book/man-port-scanning-basics.html</t>
+  </si>
+  <si>
+    <t>Useful, showed the different output formats that Nmap can have.</t>
+  </si>
+  <si>
+    <t>Very useful, explained what the different types of port states were and what they meant.</t>
+  </si>
+  <si>
+    <t>Somewhat useful, contained much of the previous source's information but with example outputs and diagrams.</t>
+  </si>
+  <si>
+    <t>Useful, showed how to read the port table, what the number, protocol, state, and service name mean.</t>
   </si>
 </sst>
 </file>
@@ -853,6 +880,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1118,7 +1149,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G116"/>
+  <dimension ref="B2:G121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1136,8 +1167,8 @@
         <v>3</v>
       </c>
       <c r="D2" s="4">
-        <f>ROUNDDOWN(SUM(C7:C503)/60,0)</f>
-        <v>31</v>
+        <f>ROUNDDOWN(SUM(C7:C502)/60,0)</f>
+        <v>32</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -1148,8 +1179,8 @@
         <v>4</v>
       </c>
       <c r="D3" s="4">
-        <f>ROUND(MOD(SUM(C7:C503),60),0)</f>
-        <v>0</v>
+        <f>ROUND(MOD(SUM(C7:C502),60),0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -2827,43 +2858,123 @@
         <v>194</v>
       </c>
     </row>
-    <row r="115" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B115" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C115" s="1">
+        <v>30</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="116" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B116" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C116" s="1">
+        <v>15</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="117" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B117" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C117" s="1">
+        <v>10</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="118" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B118" s="2">
+        <v>46303</v>
+      </c>
+      <c r="C118" s="1">
+        <v>15</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B120" s="2">
         <v>46304</v>
       </c>
-      <c r="C115" s="1">
+      <c r="C120" s="1">
         <v>15</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E115" s="1" t="s">
+      <c r="D120" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F120" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="G120" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="116" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B116" s="2">
+    <row r="121" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B121" s="2">
         <v>46304</v>
       </c>
-      <c r="C116" s="1">
+      <c r="C121" s="1">
         <v>20</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F116" s="1" t="s">
+      <c r="D121" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="G121" s="1" t="s">
         <v>202</v>
       </c>
     </row>
